--- a/assets/docs/P002_Custom_Client_Config_Template.xlsx
+++ b/assets/docs/P002_Custom_Client_Config_Template.xlsx
@@ -553,18 +553,9 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SEO Monthly Task Configuration — Custom Tier</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
+          <t>SEO Monthly Task Configuration: Custom Tier</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -572,15 +563,6 @@
           <t>Enter the number of each task type to generate per client each month. Leave blank or enter 0 for task types not included in that client's package.</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
     </row>
     <row r="3" ht="8" customHeight="1">
       <c r="A3" s="2" t="n"/>
@@ -601,21 +583,16 @@
           <t>AUTO #1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>AUTO #2</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
       <c r="H4" s="5" t="inlineStr">
         <is>
           <t>AUTO #3</t>
         </is>
       </c>
-      <c r="I4" s="4" t="n"/>
       <c r="J4" s="5" t="inlineStr">
         <is>
           <t>AUTO #4</t>
@@ -983,7 +960,7 @@
     <row r="1" ht="36" customHeight="1">
       <c r="A1" s="15" t="inlineStr">
         <is>
-          <t>SEO Monthly Task Configuration — Instructions</t>
+          <t>SEO Monthly Task Configuration: Instructions</t>
         </is>
       </c>
     </row>
